--- a/geekpractice/src/main/resources/public/workbook.xlsx
+++ b/geekpractice/src/main/resources/public/workbook.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="18">
   <si>
     <t>発注ID</t>
   </si>
@@ -565,12 +565,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="5.90625" customWidth="true" bestFit="true"/>
@@ -908,6 +946,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="19" ht="120.0" customHeight="true">
+      <c r="A19" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E19" t="n" s="0">
+        <v>46049.3540625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
